--- a/pipeline/credit_rating/output/tmr_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260924.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:33</t>
+          <t>2026-09-24 08:43:53</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">

--- a/pipeline/credit_rating/output/tmr_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/tmr_xhtn_20260924.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:53</t>
+          <t>2026-09-24 13:44:29</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
